--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63ed0a4e98b474dd/Documents/WESOke_Website/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_649064B9B696ADEF6B7F9790E2358A36B82AF7B5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D1125CE-1F64-47E4-B25F-6A309EDA8248}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>name</t>
   </si>
@@ -37,26 +43,58 @@
     <t>meganbuers_bio</t>
   </si>
   <si>
-    <t>Add your bio here - who you are, your research focus, your connection to Western Screech-Owls, and anything else you'd like visitors to know.</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
     <t>Alumni</t>
   </si>
   <si>
-    <t>Add their role and bio here.</t>
-  </si>
-  <si>
-    <t>Reese</t>
+    <t>Max Bailey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max worked as a research technician on the Coastal Western Screech-Owl Project in 2025 and 2026 supporting ARU set up and retrievals, supporting with trapping and tagging, and other field related tasks. He completed his BSc in Zoology in 2024 from the University of British Columbia Okanagan and left there with a passion for studying at- risk species and systems. Max is a lover of birds and all things nature and likes to engage with conservation regimes to help drive species protection. He can now be found birding locally around Victoria. </t>
+  </si>
+  <si>
+    <t>Reese Embree</t>
+  </si>
+  <si>
+    <r>
+      <t>Megan is a PhD student in the Quantitative Ecology Lab under the supervision of Dr. Michael Noonan and Dr. Laura Grieneisen at the University of British Columbia Okanagan. Based in Nanaimo, she is responsible for all fieldwork associated with the project. She first started working on Western Screech-owls in 2021 when she started work on her MSc on the interior subspecies of Western Screech-owls (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">M.K. macfarlanei) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">and has pivoted (although not far) to looking at impacts of landscape management and forestry on the coastal Western Screech-owls of Vancouver Island. </t>
+    </r>
+  </si>
+  <si>
+    <t>maxbailey_bio</t>
+  </si>
+  <si>
+    <t>reeseembree_bio</t>
+  </si>
+  <si>
+    <t>Reese worked as a research technician on the Coastal Western Screech-Owl Project in 2026, supporting ARU set-up and retrieval, trapping and tagging, and other field-related tasks. Reese completed her BSc Honours in Biology at the University of British Columbia Okanagan and is now pursuing an MSc through the University of Northern British Columbia, looking at wolf denning ecology.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -66,6 +104,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -104,13 +150,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -148,7 +202,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -182,6 +236,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -216,9 +271,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -391,11 +447,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="39.5703125" customWidth="1"/>
+    <col min="4" max="4" width="125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -409,7 +471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -420,29 +482,35 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63ed0a4e98b474dd/Documents/WESOke_Website/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_649064B9B696ADEF6B7F9790E2358A36B82AF7B5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D1125CE-1F64-47E4-B25F-6A309EDA8248}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="11_649064B9B696ADEF6B7F9790E2358A36B82AF7B5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{137CEA24-6864-4735-BD11-478FF4E4E7CB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>name</t>
   </si>
@@ -88,6 +88,15 @@
   </si>
   <si>
     <t>Reese worked as a research technician on the Coastal Western Screech-Owl Project in 2026, supporting ARU set-up and retrieval, trapping and tagging, and other field-related tasks. Reese completed her BSc Honours in Biology at the University of British Columbia Okanagan and is now pursuing an MSc through the University of Northern British Columbia, looking at wolf denning ecology.</t>
+  </si>
+  <si>
+    <t>Isabella Perry</t>
+  </si>
+  <si>
+    <t>issyperry_bio</t>
+  </si>
+  <si>
+    <t>Isabella is a MSc student in the Quantitative Ecology Lab supervised by Dr. Michael Noonan at the University of British Columbia’s Okanagan Campus. Isabella is passionate about connecting behavioral studies to conservation action, with her core research focusing on linking health to habitat use and selection for giant anteaters (Myrmecophaga tridactyla) in the Brazilian Cerrado. Her work with the project involves evaluating how effectively ARUs model habitat occupancy for coastal western screech-owls (Megascops kennicottii) by comparing results for acoustic data against those of GPS tracking data.</t>
   </si>
 </sst>
 </file>
@@ -159,6 +168,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -448,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
@@ -513,6 +526,20 @@
         <v>14</v>
       </c>
     </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
